--- a/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_4_['No. 63_～なら〈条件(じょうけん)〉 ']_revised_revised.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_4_['No. 63_～なら〈条件(じょうけん)〉 ']_revised_revised.xlsx
@@ -467,20 +467,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 かれは えきで ともだちに あいました。( ) は えきでした。</t>
+          <t>: もんだい1 雨が降る (   )、出かけるのをやめましょう。</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. ともだち
-2. かれ
-3. えき
-4. あいました</t>
+          <t>1. なら 2. から 3. けれど 4. ので</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -494,20 +491,17 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 わたしは まいあさ こうえんで さんぽします。( ) は こうえんです。</t>
+          <t>: もんだい1 時間がある (   )、一緒に映画を見に行きませんか。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1. まいあさ
-2. さんぽします
-3. こうえん
-4. わたし</t>
+          <t>1. から 2. なら 3. けど 4. ので</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
@@ -521,20 +515,17 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 ともだちと いっしょに レストランで たべました。( ) は レストランでした。</t>
+          <t>: もんだい1 明日が休み (   )、遊びに行こうよ。</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. ともだち
-2. いっしょに
-3. たべました
-4. レストラン</t>
+          <t>1. から 2. なら 3. けど 4. ので</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -548,20 +539,17 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 きょうは てんきが いいです。( ) は いいです。</t>
+          <t>: もんだい1 この本を読む (   )、もっと日本の歴史がわかります。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1. きょう
-2. てんき
-3. は
-4. いい</t>
+          <t>1. なら 2. けど 3. から 4. ので</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -575,20 +563,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 わたしの いえは がっこうの ちかくです。( ) は がっこうの ちかくです。</t>
+          <t>: もんだい1 彼が来る (   )、パーティーを始めましょう。</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. わたし
-2. いえ
-3. がっこう
-4. ちかく</t>
+          <t>1. なら 2. から 3. けど 4. ので</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -602,20 +587,17 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 私は朝( )ご飯を食べます。</t>
+          <t>: もんだい1 日本語を勉強する(   )、毎日練習しなければなりません。</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. あさ
-2. 朝の
-3. 朝
-4. 朝に</t>
+          <t>1. から 2. ので 3. なら 4. けど</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -629,15 +611,12 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 このかばんは( )です。</t>
+          <t>: もんだい1 行きたくない (   )、無理に行く必要はありません。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. 高い
-2. 高く
-3. 高かった
-4. 高いです</t>
+          <t>1. なら 2. から 3. けど 4. ので</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -656,20 +635,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 田中さんは日本語を( )ます。</t>
+          <t>: もんだい1 天気がいい (   )、ピクニックに行きましょう。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. 話
-2. 話して
-3. 話す
-4. 話した</t>
+          <t>1. なら 2. けど 3. から 4. ので</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -683,20 +659,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 学校に( )ます。</t>
+          <t>: もんだい1 お金が足りない (   )、買い物を控えよう。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. 行
-2. 行って
-3. 行く
-4. 行った</t>
+          <t>1. なら 2. けど 3. から 4. ので</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -710,17 +683,17 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨がふる (   )、かさを もって いきます。</t>
+          <t>: もんだい2 雨がふる(   )、かさをもっていきます。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. に 3. が 4. を</t>
+          <t>1. なら 2. とき 3. が 4. を</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -729,12 +702,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が ある (   )、一緒に 映画を 見に 行きませんか。</t>
+          <t>: もんだい2 時間が ある (   )、一緒に 映画を 見に 行きませんか。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -753,12 +726,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 日本に 行く (   )、お土産を 買って きます。</t>
+          <t>: もんだい2 日本に 行く (   )、お土産を 買って きます。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -777,12 +750,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お茶が 好き (   )、この店の お茶を 飲んで みて。</t>
+          <t>: もんだい2 お茶が 好き (   )、この店の お茶を 飲んで みて。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -801,12 +774,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 明日 雨が 降る (   )、ピクニックは 中止です。</t>
+          <t>: もんだい2 明日 雨が 降る (   )、ピクニックは 中止です。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -825,12 +798,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 この本を 読む (   )、辞書が 必要です。</t>
+          <t>: もんだい2 この本を 読む (   )、辞書が 必要です。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -849,12 +822,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 時間が かかる (   )、タクシーを 使いましょう。</t>
+          <t>: もんだい2 時間が かかる (   )、タクシーを 使いましょう。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -873,12 +846,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 旅行に 行く (   )、パスポートを 忘れないで。</t>
+          <t>: もんだい2 旅行に 行く (   )、パスポートを 忘れないで。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -897,12 +870,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 彼が 来る (   )、パーティーを 始めましょう。</t>
+          <t>: もんだい2 彼が 来る (   )、パーティーを 始めましょう。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -921,12 +894,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 お金が 足りない (   )、友達に 借りよう。</t>
+          <t>: もんだい2 お金が 足りない (   )、友達に 借りよう。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -945,22 +918,22 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金がないなら、もっと(   )。</t>
+          <t>: もんだい3 お金がないなら、もっと(   )。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>1. 働く 2. 働けば 3. 働きなさい 4. 働いて</t>
+          <t>1. 働く 2. 働けば 3. 働きなさい 4. 働こう</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr"/>
@@ -969,12 +942,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 雨が降るなら、(   )。</t>
+          <t>: もんだい3 雨が降るなら、(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -993,12 +966,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 暇(ひま)なら、映画を(   )。</t>
+          <t>: もんだい3 暇(ひま)なら、映画を(   )。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1017,12 +990,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 彼女が来るなら、(   )。</t>
+          <t>: もんだい3 彼女が来るなら、(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1041,12 +1014,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 安いなら、この服を(   )。</t>
+          <t>: もんだい3 安いなら、この服を(   )。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1065,12 +1038,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 時間があるなら、(   )。</t>
+          <t>: もんだい3 時間があるなら、(   )。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1089,12 +1062,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 日本に行くなら、(   )。</t>
+          <t>: もんだい3 日本に行くなら、(   )。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1113,12 +1086,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 彼が忙しいなら、(   )。</t>
+          <t>: もんだい3 彼が忙しいなら、(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1137,12 +1110,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 試験があるなら、(   )。</t>
+          <t>: もんだい3 試験があるなら、(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1161,22 +1134,22 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 部屋が寒いなら、(   )。</t>
+          <t>: もんだい3 部屋が寒いなら、(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. 暖房をつける 2. 暖房をつけて 3. 暖房をつけよう 4. 暖房をつけない</t>
+          <t>1. 暖房をつける 2. 暖房をつけた 3. 暖房をつけて 4. 暖房をつけよう</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr"/>
@@ -1185,22 +1158,22 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 明日 雨が 降るなら、 わたしは 家に (   ).</t>
+          <t>: もんだい4 もし明日雨が降るなら、わたしは家に(   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>1. いよう 2. いきたい 3. いく 4. いっている</t>
+          <t>1. いよう 2. いたい 3. いる 4. いった</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr"/>
@@ -1209,12 +1182,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 映画館で いい映画が やっているなら、 みんなで (   ).</t>
+          <t>: もんだい4 映画館で いい映画が やっているなら、 みんなで (   )。</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1233,12 +1206,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼が パーティーに 来るなら、 私も (   ).</t>
+          <t>: もんだい4 彼が パーティーに 来るなら、 私も (   ).</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1257,12 +1230,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 日本料理が 好きなら、 このレストランを (   ).</t>
+          <t>: もんだい4 もし 日本料理が 好きなら、 このレストランを (   ).</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1281,12 +1254,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 時間が あるなら、 一緒に (   ).</t>
+          <t>: もんだい4 もし 時間が あるなら、 一緒に (   ).</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1305,12 +1278,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 新しいカフェが オープンするなら、 週末に (   ).</t>
+          <t>: もんだい4 新しいカフェが オープンするなら、 週末に (   ).</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1329,12 +1302,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼女が その本を 読んでいるなら、 私も (   ).</t>
+          <t>: もんだい4 もし 彼女が その本を 読んでいるなら、 私も (   ).</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1353,12 +1326,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 お金が たくさん あるなら、 世界旅行を (   ).</t>
+          <t>: もんだい4 お金が たくさん あるなら、 世界旅行を (   ).</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1377,12 +1350,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 彼が 行くなら、 私も (   )。</t>
+          <t>: もんだい4 もし 彼が 行くなら、 私も (   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1401,22 +1374,22 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼女が 料理を 作るなら、 私も 手伝おうと (   ).</t>
+          <t>: もんだい4 彼女が料理を作るなら、私も手伝おうと(   )。</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. 思う 2. 決めた 3. 思っている 4. 思った</t>
+          <t>1. 思う 2. 思った 3. 思っている 4. 思いながら</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr"/>
@@ -1425,12 +1398,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 このりんごが安いなら、(   )。</t>
+          <t>: もんだい5 このりんごが安いなら、(   )。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1449,12 +1422,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が来るなら、(   )。</t>
+          <t>: もんだい5 彼が来るなら、(   )。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1473,12 +1446,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降るなら、(   )。</t>
+          <t>: もんだい5 雨が降るなら、(   )。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1497,12 +1470,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 カレーを作るなら、(   )。</t>
+          <t>: もんだい5 カレーを作るなら、(   )。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1521,12 +1494,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼女が好きなら、(   )。</t>
+          <t>: もんだい5 彼女が好きなら、(   )。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1545,12 +1518,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 試験が難しいなら、(   )。</t>
+          <t>: もんだい5 試験が難しいなら、(   )。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1569,12 +1542,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 旅行に行くなら、(   )。</t>
+          <t>: もんだい5 旅行に行くなら、(   )。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1593,12 +1566,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この映画が面白いなら、(   )。</t>
+          <t>: もんだい5 この映画が面白いなら、(   )。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1617,12 +1590,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が先生なら、(   )。</t>
+          <t>: もんだい5 彼が先生なら、(   )。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1641,12 +1614,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 日本に住むなら、(   )。</t>
+          <t>: もんだい5 日本に住むなら、(   )。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1665,12 +1638,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「このレストランは美味しいですか。 」 B:「はい、美味しいですよ。 もし行く(   )、予約をしたほうがいいですよ。 」</t>
+          <t>: もんだい6 A:「このレストランは美味しいですか。」 B:「はい、美味しいですよ。もし行く(   )、予約をしたほうがいいですよ。」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1689,12 +1662,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「田中さん、映画を見に行きませんか。 」 B:「映画ですか。 時間がある(   )、ぜひ行きたいです。 」</t>
+          <t>: もんだい6 A:「田中さん、映画を見に行きませんか。」 B:「映画ですか。時間がある(   )、ぜひ行きたいです。」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1713,12 +1686,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「もし、かぜをひいた(   )、この薬を飲んでください。 」 B:「はい、わかりました。 」</t>
+          <t>: もんだい6 A:「もし、かぜをひいた(   )、この薬を飲んでください。」 B:「はい、わかりました。」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1737,22 +1710,22 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「スキーが好きですか。 」 B:「はい、好きです。 でも、雪がたくさん降る(   )、行きたくないです。 」</t>
+          <t>: もんだい6 A:「スキーが好きですか。」 B:「はい、好きです。でも、雪がたくさん降る(   )、行きたくないです。」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. と 3. から 4. ので</t>
+          <t>1. なら 2. とき 3. から 4. ので</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr"/>
@@ -1761,22 +1734,22 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この本を読みたいですか。 」 B:「読みたいですが、面白くない(   )、読みません。 」</t>
+          <t>: もんだい6 A:「この本を読みたいですか。」 B:「読みたいですが、面白くない(   )、読みません。」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. から 3. と 4. ので</t>
+          <t>1. なら 2. から 3. とき 4. ので</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr"/>
@@ -1785,17 +1758,17 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「旅行に行きたいですね。 」 B:「そうですね。 もし、お金がたくさんある(   )、ヨーロッパに行きたいです。 」</t>
+          <t>: もんだい6 A:「旅行に行きたいですね。」 B:「そうですね。もし、お金がたくさんある(   )、ヨーロッパに行きたいです。」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. から 3. と 4. ので</t>
+          <t>1. なら 2. から 3. とき 4. ので</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -1809,22 +1782,25 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「明日、雨が降る(   )、ピクニックは中止しましょう。 」 B:「そうですね、準備が必要ですね。 」</t>
+          <t>: もんだい6 A:「明日、雨が降る(   )、ピクニックは中止しましょう。」 B:「そうですね、準備が必要ですね。」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. から 3. と 4. ので</t>
+          <t>1. なら
+2. とき
+3. から
+4. ので</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr"/>
@@ -1833,22 +1809,25 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この問題が難しいですか。 」 B:「はい、難しいです。 でも、先生に聞く(   )、わかると思います。 」</t>
+          <t>: もんだい6 A:「この問題が難しいですか。」 B:「はい、難しいです。でも、先生に聞く(   )、わかると思います。」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. から 3. と 4. ので</t>
+          <t>1. なら
+2. とき
+3. たら
+4. ので</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
@@ -1857,17 +1836,17 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「しゅくだいを手伝ってくれませんか。 」 B:「いいですよ。 私でよければ、手伝う(   )。 」</t>
+          <t>: もんだい6 A:「しゅくだいを手伝ってくれませんか。」 B:「いいですよ。私でよければ、手伝う(   )。」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. から 3. と 4. ので</t>
+          <t>1. なら 2. とき 3. から 4. ので</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -1881,17 +1860,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「新しいパソコンが欲しいですね。 」 B:「ええ、もし安く買える(   )、すぐに買いたいです。 」</t>
+          <t>: もんだい6 A:「新しいパソコンが欲しいですね。」 B:「ええ、もし安く買える(   )、すぐに買いたいです。」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>1. なら 2. から 3. と 4. ので</t>
+          <t>1. なら 2. とき 3. から 4. ので</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -1905,12 +1884,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 映画を見るなら、(   )。</t>
+          <t>: もんだい7 映画を見るなら、(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1929,12 +1908,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 雨が降るなら、(   )。</t>
+          <t>: もんだい7 雨が降るなら、(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1953,12 +1932,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 日本語を勉強するなら、(   )。</t>
+          <t>: もんだい7 日本語を勉強するなら、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1977,12 +1956,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 行かないなら、(   )。</t>
+          <t>: もんだい7 行かないなら、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2001,12 +1980,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼が来るなら、(   )。</t>
+          <t>: もんだい7 彼が来るなら、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2025,12 +2004,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼女が行かないなら、(   )。</t>
+          <t>: もんだい7 彼女が行かないなら、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2049,12 +2028,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 勉強しないなら、(   )。</t>
+          <t>: もんだい7 勉強しないなら、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2073,12 +2052,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 行くなら、(   )。</t>
+          <t>: もんだい7 行くなら、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2097,12 +2076,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 彼が手伝うなら、(   )。</t>
+          <t>: もんだい7 彼が手伝うなら、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2121,12 +2100,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 日本に行くなら、(   )。</t>
+          <t>: もんだい7 日本に行くなら、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2145,12 +2124,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし 天気 (てんき) が いい (   )、公園 (こうえん) に 行きましょう。</t>
+          <t>: もんだい8 もし 天気 (てんき) が いい (   )、公園 (こうえん) に 行きましょう。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2169,22 +2148,22 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 その 本 (ほん) を 読んだ (   )、感想 (かんそう) を 教えてください。</t>
+          <t>: もんだい8 その本を読んだ(   )、感想を教えてください。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>1. みたい 2. なら 3. らしく 4. ように</t>
+          <t>1. みたい 2. らしく 3. ように 4. たら</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr"/>
@@ -2193,17 +2172,17 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 時間 (じかん) が ある (   )、手伝って (てつだって) もらえますか。</t>
+          <t>: もんだい8 時間がある(   )、手伝ってもらえますか。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>1. らしく 2. なら 3. ほどに 4. ように</t>
+          <t>1. らしく 2. とき 3. ほどに 4. ように</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
@@ -2217,12 +2196,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 カメラを 使う (つかう) (   )、説明書 (せつめいしょ) を 読んでください。</t>
+          <t>: もんだい8 カメラを使う(   )、説明書を読んでください。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2241,12 +2220,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし 雨 (あめ) が 降らない (   )、試合 (しあい) は 外 (そと) で 行います。</t>
+          <t>: もんだい8 もし雨が降らない(   )、試合は外で行います。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2265,17 +2244,17 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この 映画 (えいが) を 見る (   )、泣いて (ないて) しまうかも。</t>
+          <t>: もんだい8 この映画を見る(   )、泣いてしまうかも。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>1. らしく 2. みたい 3. なら 4. ように</t>
+          <t>1. らしく 2. みたい 3. と 4. ように</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -2289,12 +2268,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 もし 時間 (じかん) が ない (   )、無理 (むり) しないでください。</t>
+          <t>: もんだい8 もし時間がない(   )、無理しないでください。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2313,12 +2292,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 英語 (えいご) が 上手 (じょうず) なら (   )、通訳 (つうやく) になれます。</t>
+          <t>: もんだい8 英語が上手なら、(   )、通訳になれます。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2337,12 +2316,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 その 問題 (もんだい) が 解決 (かいけつ) できる (   )、すぐに 連絡 (れんらく) します。</t>
+          <t>: もんだい8 その問題が解決できる(   )、すぐに連絡します。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2361,12 +2340,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 彼 (かれ) が 来る (   )、パーティーを 始めましょう。</t>
+          <t>: もんだい8 彼が来る(   )、パーティーを始めましょう。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
